--- a/data/trending_integrated_20261029_15.xlsx
+++ b/data/trending_integrated_20261029_15.xlsx
@@ -567,18 +567,18 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5020</v>
+        <v>5110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.57%</t>
+          <t>'+29.86%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
         <v>27</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>8392849503</v>
+        <v>8554158780</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49650</v>
+        <v>48400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+23.51%</t>
+          <t>'+20.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F3" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G3" t="n">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="H3" t="n">
         <v>24.64</v>
@@ -702,7 +702,7 @@
         <v>24.63</v>
       </c>
       <c r="O3" t="n">
-        <v>100796981550</v>
+        <v>106495642775</v>
       </c>
       <c r="P3" t="n">
         <v>97900</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9490</v>
+        <v>9370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.77%</t>
+          <t>'+17.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H4" t="n">
         <v>17.97</v>
@@ -794,7 +794,7 @@
         <v>18.64</v>
       </c>
       <c r="O4" t="n">
-        <v>141517462940</v>
+        <v>144131161695</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -886,7 +886,7 @@
         <v>6.54</v>
       </c>
       <c r="O5" t="n">
-        <v>119553452025</v>
+        <v>120802717225</v>
       </c>
       <c r="P5" t="n">
         <v>126600</v>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7820</v>
+        <v>7830</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.97%</t>
+          <t>'+5.10%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="H6" t="n">
         <v>0.42</v>
@@ -978,7 +978,7 @@
         <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>114157174025</v>
+        <v>114608517710</v>
       </c>
       <c r="P6" t="n">
         <v>10300</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광주 반도체 테마와 연계된 상승 기대감. 외국인 및 기타 법인 매수세 유입으로 인한 주가 상승 전망.</t>
+          <t>광주 반도체 테마 편입 및 외국인 매수세 유입. 단기 급등 후 차익 실현.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광주 반도체', '테마주', '외국인 매수']</t>
+          <t>['광주 반도체', '외국인 매수', '테마주']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>루닛</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1543000</v>
+        <v>14990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+4.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>147</v>
       </c>
       <c r="F7" t="n">
-        <v>491</v>
+        <v>83</v>
       </c>
       <c r="G7" t="n">
-        <v>1942</v>
+        <v>425</v>
       </c>
       <c r="H7" t="n">
-        <v>48.66</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1487000</v>
+        <v>14390</v>
       </c>
       <c r="K7" t="n">
-        <v>1511000</v>
+        <v>15450</v>
       </c>
       <c r="L7" t="n">
-        <v>1587000</v>
+        <v>16290</v>
       </c>
       <c r="M7" t="n">
-        <v>1479000</v>
+        <v>14040</v>
       </c>
       <c r="N7" t="n">
-        <v>48.61</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>6147212844000</v>
+        <v>63935941300</v>
       </c>
       <c r="P7" t="n">
-        <v>2987000</v>
+        <v>49800</v>
       </c>
       <c r="Q7" t="n">
-        <v>501000</v>
+        <v>8180</v>
       </c>
       <c r="R7" t="n">
-        <v>374000</v>
+        <v>-273000</v>
       </c>
       <c r="S7" t="n">
-        <v>-115000</v>
+        <v>-15000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>자사주 매입 발표 및 외국인 순매수로 인한 긍정적 시장 반응. 삼성전자 대비 우위 평가.</t>
+          <t>미국 의료AI 및 템퍼스AI 급등에 따른 국내 시장 시초 상승 기대감. 매수/매도 의견 혼재 및 단기적 가격 변동성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인순매수', '수급']</t>
+          <t>['의료AI', '차트', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>328130</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14800</v>
+        <v>1522000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.85%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>140</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="G8" t="n">
-        <v>418</v>
+        <v>2012</v>
       </c>
       <c r="H8" t="n">
-        <v>8.050000000000001</v>
+        <v>48.66</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14390</v>
+        <v>1487000</v>
       </c>
       <c r="K8" t="n">
-        <v>15450</v>
+        <v>1511000</v>
       </c>
       <c r="L8" t="n">
-        <v>16290</v>
+        <v>1587000</v>
       </c>
       <c r="M8" t="n">
-        <v>14040</v>
+        <v>1479000</v>
       </c>
       <c r="N8" t="n">
-        <v>8.109999999999999</v>
+        <v>48.61</v>
       </c>
       <c r="O8" t="n">
-        <v>62351240820</v>
+        <v>6297305458500</v>
       </c>
       <c r="P8" t="n">
-        <v>49800</v>
+        <v>2987000</v>
       </c>
       <c r="Q8" t="n">
-        <v>8180</v>
+        <v>501000</v>
       </c>
       <c r="R8" t="n">
-        <v>-273000</v>
+        <v>374000</v>
       </c>
       <c r="S8" t="n">
-        <v>-15000</v>
+        <v>-115000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>의료 AI 관련 종목 강세 속에서도 개인 투자자들의 매도 압력 및 공매도 관련 언급.</t>
+          <t>자사주 매입 통한 주가 부양 노력. 삼성전자 대비 선방 및 긍정적 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['의료AI', '공매도', '매도압력']</t>
+          <t>['자사주 매입', '주가 부양', '수급']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>328130</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
         <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H9" t="n">
         <v>1.77</v>
@@ -1254,7 +1254,7 @@
         <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>111124814250</v>
+        <v>112032080050</v>
       </c>
       <c r="P9" t="n">
         <v>59600</v>
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>538000</v>
+        <v>15020</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.75%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>388</v>
+        <v>166</v>
       </c>
       <c r="F10" t="n">
-        <v>189</v>
+        <v>96</v>
       </c>
       <c r="G10" t="n">
-        <v>1894</v>
+        <v>1038</v>
       </c>
       <c r="H10" t="n">
-        <v>24.78</v>
+        <v>3.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>534000</v>
+        <v>14980</v>
       </c>
       <c r="K10" t="n">
-        <v>546000</v>
+        <v>15120</v>
       </c>
       <c r="L10" t="n">
-        <v>563000</v>
+        <v>15950</v>
       </c>
       <c r="M10" t="n">
-        <v>512000</v>
+        <v>14600</v>
       </c>
       <c r="N10" t="n">
-        <v>24.86</v>
+        <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>566448728000</v>
+        <v>154482426175</v>
       </c>
       <c r="P10" t="n">
-        <v>723000</v>
+        <v>31500</v>
       </c>
       <c r="Q10" t="n">
-        <v>259000</v>
+        <v>1819</v>
       </c>
       <c r="R10" t="n">
-        <v>-36000</v>
+        <v>-444000</v>
       </c>
       <c r="S10" t="n">
-        <v>35000</v>
+        <v>44000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
+          <t>메타 및 유리기판 관련 뉴스 부각. 삼성전자 인수 기대감 및 연기금 매집.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
+          <t>['유리기판', '삼성전자', '연기금']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15030</v>
+        <v>535000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.19%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>165</v>
+        <v>395</v>
       </c>
       <c r="F11" t="n">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="G11" t="n">
-        <v>1004</v>
+        <v>1905</v>
       </c>
       <c r="H11" t="n">
-        <v>3.33</v>
+        <v>24.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>14980</v>
+        <v>534000</v>
       </c>
       <c r="K11" t="n">
-        <v>15120</v>
+        <v>546000</v>
       </c>
       <c r="L11" t="n">
-        <v>15950</v>
+        <v>563000</v>
       </c>
       <c r="M11" t="n">
-        <v>14600</v>
+        <v>512000</v>
       </c>
       <c r="N11" t="n">
-        <v>2.87</v>
+        <v>24.86</v>
       </c>
       <c r="O11" t="n">
-        <v>153512606465</v>
+        <v>578539099500</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>723000</v>
       </c>
       <c r="Q11" t="n">
-        <v>1819</v>
+        <v>259000</v>
       </c>
       <c r="R11" t="n">
-        <v>-444000</v>
+        <v>-36000</v>
       </c>
       <c r="S11" t="n">
-        <v>44000</v>
+        <v>35000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>메타버스 관련 뉴스 및 3분기 실적 전망에 따른 상승 기대감. 루멘텀 관련 언급.</t>
+          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메타버스', '실적전망', '루멘텀']</t>
+          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>186300</v>
+        <v>62900</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.00%</t>
+          <t>'-2.02%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1</v>
+        <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>158</v>
       </c>
       <c r="F12" t="n">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>626</v>
+        <v>779</v>
       </c>
       <c r="H12" t="n">
-        <v>75</v>
+        <v>41.55</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>190100</v>
+        <v>64200</v>
       </c>
       <c r="K12" t="n">
-        <v>189400</v>
+        <v>64200</v>
       </c>
       <c r="L12" t="n">
-        <v>197000</v>
+        <v>65500</v>
       </c>
       <c r="M12" t="n">
-        <v>180800</v>
+        <v>62400</v>
       </c>
       <c r="N12" t="n">
-        <v>74.90000000000001</v>
+        <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>1481145710300</v>
+        <v>192448663350</v>
       </c>
       <c r="P12" t="n">
-        <v>243500</v>
+        <v>67300</v>
       </c>
       <c r="Q12" t="n">
-        <v>71000</v>
+        <v>23150</v>
       </c>
       <c r="R12" t="n">
-        <v>-1382000</v>
+        <v>273000</v>
       </c>
       <c r="S12" t="n">
-        <v>-119000</v>
+        <v>-191000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>우선주 매입 소각 및 주주환원 결정 지연에 대한 불만. 오너 리스크와 허술한 IR 대응에 대한 비판.</t>
+          <t>수주 공시 및 신고가 근접. 자사주 매입 통한 공매도 방어.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['우선주', '주주환원', 'IR']</t>
+          <t>['수주 공시', '신고가', '자사주 매입']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62500</v>
+        <v>184700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.65%</t>
+          <t>'-2.84%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.54</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="F13" t="n">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="G13" t="n">
-        <v>767</v>
+        <v>641</v>
       </c>
       <c r="H13" t="n">
-        <v>41.55</v>
+        <v>75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>64200</v>
+        <v>190100</v>
       </c>
       <c r="K13" t="n">
-        <v>64200</v>
+        <v>189400</v>
       </c>
       <c r="L13" t="n">
-        <v>65500</v>
+        <v>197000</v>
       </c>
       <c r="M13" t="n">
-        <v>62400</v>
+        <v>180800</v>
       </c>
       <c r="N13" t="n">
-        <v>41.01</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>186978555700</v>
+        <v>1510897744550</v>
       </c>
       <c r="P13" t="n">
-        <v>67300</v>
+        <v>243500</v>
       </c>
       <c r="Q13" t="n">
-        <v>23150</v>
+        <v>71000</v>
       </c>
       <c r="R13" t="n">
-        <v>273000</v>
+        <v>-1382000</v>
       </c>
       <c r="S13" t="n">
-        <v>-191000</v>
+        <v>-119000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>수주 공시 및 신고가 도전 기대감. 자사주 매입을 통한 주가 방어 및 수소 시대 성장 전망.</t>
+          <t>오너 리스크 및 IR 부실에 대한 불만. 주주 환원 정책 불확실성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['수주공시', '자사주매입', '수소시대']</t>
+          <t>['오너 리스크', 'IR 부실', '주주 환원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8910</v>
+        <v>8890</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.94%</t>
+          <t>'-3.16%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1714,7 +1714,7 @@
         <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>31453969980</v>
+        <v>31554032230</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4047</v>
+        <v>4030</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.53%</t>
+          <t>'-3.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="H15" t="n">
         <v>2.2</v>
@@ -1806,7 +1806,7 @@
         <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>172891414455</v>
+        <v>173991427504</v>
       </c>
       <c r="P15" t="n">
         <v>8100</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>232500</v>
+        <v>232000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-4.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G16" t="n">
-        <v>2954</v>
+        <v>2921</v>
       </c>
       <c r="H16" t="n">
         <v>46.19</v>
@@ -1898,7 +1898,7 @@
         <v>46.15</v>
       </c>
       <c r="O16" t="n">
-        <v>5158891712750</v>
+        <v>5283799379250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>주주환원 결정 지연 및 경영진 관련 논란으로 인한 부정적 전망. 컨퍼런스콜 내용 비판.</t>
+          <t>이사회 결정에 대한 불만 고조. 주주 환원 지연 및 증여세 관련 의혹 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '컨퍼런스콜', '경영진']</t>
+          <t>['주주 환원', '증여세', '이사회 결정']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15670</v>
+        <v>15730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.09%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G17" t="n">
-        <v>688</v>
+        <v>701</v>
       </c>
       <c r="H17" t="n">
         <v>28.07</v>
@@ -1990,7 +1990,7 @@
         <v>28.03</v>
       </c>
       <c r="O17" t="n">
-        <v>75777129625</v>
+        <v>78765790300</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 발표 후에도 주가 하락 지속에 대한 불만. 공매도 관련 언급 및 일부 긍정적 실적 지표.</t>
+          <t>실적 및 수주 공시에도 불구하고 주가 하락 지속. 조선주 동반 약세.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '주가하락', '공매도']</t>
+          <t>['실적 발표', '수주 공시', '주가 하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>16726018976</v>
+        <v>18945599499</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56300</v>
+        <v>56600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-8.31%</t>
+          <t>'-7.82%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="G19" t="n">
-        <v>2272</v>
+        <v>2270</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>417204318800</v>
+        <v>424364076650</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>허위 기사 및 풍문에 대한 해명 공시 발표 후 주가 회복 기대. 기자 고소 및 계약 관련 논란.</t>
+          <t>체코 원전 입찰 관련 허위 기사 논란. 해명 공시 후 주가 회복 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['해명공시', '풍문', '계약']</t>
+          <t>['체코 원전', '허위 기사', '해명 공시']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,79 +2219,79 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16920</v>
+        <v>23600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-11.92%</t>
+          <t>'-11.61%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.46</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>206</v>
+        <v>335</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="G20" t="n">
-        <v>192</v>
+        <v>836</v>
       </c>
       <c r="H20" t="n">
-        <v>0.65</v>
+        <v>12.23</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>19210</v>
+        <v>26700</v>
       </c>
       <c r="K20" t="n">
-        <v>19010</v>
+        <v>26350</v>
       </c>
       <c r="L20" t="n">
-        <v>19840</v>
+        <v>26600</v>
       </c>
       <c r="M20" t="n">
-        <v>16280</v>
+        <v>23300</v>
       </c>
       <c r="N20" t="n">
-        <v>1.11</v>
+        <v>12.3</v>
       </c>
       <c r="O20" t="n">
-        <v>104959320145</v>
+        <v>143932163275</v>
       </c>
       <c r="P20" t="n">
-        <v>28800</v>
+        <v>59300</v>
       </c>
       <c r="Q20" t="n">
-        <v>11550</v>
+        <v>22000</v>
       </c>
       <c r="R20" t="n">
-        <v>20000</v>
+        <v>-394000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회에 따른 급락 및 하락 전망. 주포의 의도에 대한 의구심.</t>
+          <t>실적 발표 후 주가 하락에 대한 불만. 미 증시 태양광 하락 영향.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['보호예수', '하락', '주포']</t>
+          <t>['실적 발표', '주가 하락', '태양광']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,86 +2304,86 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23450</v>
+        <v>16800</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-12.17%</t>
+          <t>'-12.55%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="E21" t="n">
-        <v>302</v>
+        <v>205</v>
       </c>
       <c r="F21" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="G21" t="n">
-        <v>731</v>
+        <v>195</v>
       </c>
       <c r="H21" t="n">
-        <v>12.23</v>
+        <v>0.65</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>26700</v>
+        <v>19210</v>
       </c>
       <c r="K21" t="n">
-        <v>26350</v>
+        <v>19010</v>
       </c>
       <c r="L21" t="n">
-        <v>26600</v>
+        <v>19840</v>
       </c>
       <c r="M21" t="n">
-        <v>23450</v>
+        <v>16280</v>
       </c>
       <c r="N21" t="n">
-        <v>12.3</v>
+        <v>1.11</v>
       </c>
       <c r="O21" t="n">
-        <v>131259485175</v>
+        <v>105807335690</v>
       </c>
       <c r="P21" t="n">
-        <v>59300</v>
+        <v>28800</v>
       </c>
       <c r="Q21" t="n">
-        <v>22000</v>
+        <v>11550</v>
       </c>
       <c r="R21" t="n">
-        <v>-394000</v>
+        <v>20000</v>
       </c>
       <c r="S21" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 발표 예정 속 기관/외인 매도세 및 하락 추세에 대한 우려. 일부 긍정적 전망 존재.</t>
+          <t>보호예수 물량 출회에 따른 급락 및 하락 전망. 주포의 의도에 대한 의구심.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적발표', '매도세', '전망']</t>
+          <t>['보호예수', '하락', '주포']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.70%</t>
+          <t>'-17.90%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G22" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>17403263064</v>
+        <v>17550097863</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11650</v>
+        <v>11670</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-18.36%</t>
+          <t>'-18.22%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="G23" t="n">
-        <v>2420</v>
+        <v>2415</v>
       </c>
       <c r="H23" t="n">
         <v>9.6</v>
@@ -2542,7 +2542,7 @@
         <v>9.83</v>
       </c>
       <c r="O23" t="n">
-        <v>356760418135</v>
+        <v>361504485405</v>
       </c>
       <c r="P23" t="n">
         <v>40350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>체코 원전 사업 재협상 관련 부정적 전망과 정치권 개입 의혹 제기. 외인 매수세에도 불구하고 주가 하락세 지속.</t>
+          <t>체코 원전 수주 불발에 따른 반사 이익 기대감. 정치권 개입 및 협상 과정에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['체코 원전', '재협상', '정치권 개입']</t>
+          <t>['체코 원전', '수주 불발', '정치권 개입']</t>
         </is>
       </c>
       <c r="X23" t="n">

--- a/data/trending_integrated_20261029_15.xlsx
+++ b/data/trending_integrated_20261029_15.xlsx
@@ -584,7 +584,7 @@
         <v>27</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H2" t="n">
         <v>0.62</v>
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>8554158780</v>
+        <v>8562406320</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>48400</v>
+        <v>49200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+20.40%</t>
+          <t>'+22.39%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F3" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3" t="n">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="H3" t="n">
         <v>24.64</v>
@@ -702,7 +702,7 @@
         <v>24.63</v>
       </c>
       <c r="O3" t="n">
-        <v>106495642775</v>
+        <v>109033959475</v>
       </c>
       <c r="P3" t="n">
         <v>97900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>어닝 서프라이즈급 실적 발표 및 하이브리드 본더 시장 장악 기대감. 역대급 실적 전망.</t>
+          <t>창사 이래 역대급 실적 발표. 영업이익 및 분기이익 급증. 하이브리드 본더 시장 확대 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['어닝서프라이즈', '실적', '하이브리드본더']</t>
+          <t>['실적', '영업이익', '하이브리드본더']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9370</v>
+        <v>9390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.27%</t>
+          <t>'+17.52%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H4" t="n">
         <v>17.97</v>
@@ -794,7 +794,7 @@
         <v>18.64</v>
       </c>
       <c r="O4" t="n">
-        <v>144131161695</v>
+        <v>144937493540</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38000</v>
+        <v>37950</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.20%</t>
+          <t>'+9.05%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -886,7 +886,7 @@
         <v>6.54</v>
       </c>
       <c r="O5" t="n">
-        <v>120802717225</v>
+        <v>121643732600</v>
       </c>
       <c r="P5" t="n">
         <v>126600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7830</v>
+        <v>7880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.10%</t>
+          <t>'+5.77%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.04</v>
       </c>
       <c r="E6" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F6" t="n">
         <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="H6" t="n">
         <v>0.42</v>
@@ -978,7 +978,7 @@
         <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>114608517710</v>
+        <v>115168674705</v>
       </c>
       <c r="P6" t="n">
         <v>10300</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14990</v>
+        <v>14950</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+3.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F7" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>425</v>
+        <v>442</v>
       </c>
       <c r="H7" t="n">
         <v>8.050000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>63935941300</v>
+        <v>64405912605</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 의료AI 및 템퍼스AI 급등에 따른 국내 시장 시초 상승 기대감. 매수/매도 의견 혼재 및 단기적 가격 변동성 언급.</t>
+          <t>의료 AI 관련 미국 시장 급등 영향. 매수 구간 진입 및 공매도 청산 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료AI', '차트', '공매도']</t>
+          <t>['의료AI', '나스닥', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1522000</v>
+        <v>1520000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>486</v>
       </c>
       <c r="G8" t="n">
-        <v>2012</v>
+        <v>1996</v>
       </c>
       <c r="H8" t="n">
         <v>48.66</v>
@@ -1162,7 +1162,7 @@
         <v>48.61</v>
       </c>
       <c r="O8" t="n">
-        <v>6297305458500</v>
+        <v>6389597865500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 통한 주가 부양 노력. 삼성전자 대비 선방 및 긍정적 전망.</t>
+          <t>자사주 매입 결정 및 외국인 연일 매수세 유입. 공매도 불가 및 주주 친화적 결정 긍정적 평가.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주 매입', '주가 부양', '수급']</t>
+          <t>['자사주매입', '외국인매수', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H9" t="n">
         <v>1.77</v>
@@ -1254,7 +1254,7 @@
         <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>112032080050</v>
+        <v>112478279900</v>
       </c>
       <c r="P9" t="n">
         <v>59600</v>
@@ -1314,13 +1314,13 @@
         <v>0.46</v>
       </c>
       <c r="E10" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F10" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G10" t="n">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="H10" t="n">
         <v>3.33</v>
@@ -1346,7 +1346,7 @@
         <v>2.87</v>
       </c>
       <c r="O10" t="n">
-        <v>154482426175</v>
+        <v>155172036050</v>
       </c>
       <c r="P10" t="n">
         <v>31500</v>
@@ -1406,13 +1406,13 @@
         <v>-0.08</v>
       </c>
       <c r="E11" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F11" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G11" t="n">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="H11" t="n">
         <v>24.78</v>
@@ -1438,7 +1438,7 @@
         <v>24.86</v>
       </c>
       <c r="O11" t="n">
-        <v>578539099500</v>
+        <v>583257084500</v>
       </c>
       <c r="P11" t="n">
         <v>723000</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62900</v>
+        <v>62800</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-2.02%</t>
+          <t>'-2.18%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G12" t="n">
-        <v>779</v>
+        <v>800</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>192448663350</v>
+        <v>196162126850</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>184700</v>
+        <v>8880</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-2.84%</t>
+          <t>'-3.27%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>-0.37</v>
       </c>
       <c r="E13" t="n">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
-        <v>124</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>641</v>
+        <v>210</v>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
+        <v>0.37</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>190100</v>
+        <v>9180</v>
       </c>
       <c r="K13" t="n">
-        <v>189400</v>
+        <v>9200</v>
       </c>
       <c r="L13" t="n">
-        <v>197000</v>
+        <v>10900</v>
       </c>
       <c r="M13" t="n">
-        <v>180800</v>
+        <v>8730</v>
       </c>
       <c r="N13" t="n">
-        <v>74.90000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1510897744550</v>
+        <v>31680390985</v>
       </c>
       <c r="P13" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>71000</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-1382000</v>
+        <v>-40000</v>
       </c>
       <c r="S13" t="n">
-        <v>-119000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>오너 리스크 및 IR 부실에 대한 불만. 주주 환원 정책 불확실성.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['오너 리스크', 'IR 부실', '주주 환원']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8890</v>
+        <v>183800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-3.31%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.37</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>193</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="G14" t="n">
-        <v>210</v>
+        <v>646</v>
       </c>
       <c r="H14" t="n">
-        <v>0.37</v>
+        <v>75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9180</v>
+        <v>190100</v>
       </c>
       <c r="K14" t="n">
-        <v>9200</v>
+        <v>189400</v>
       </c>
       <c r="L14" t="n">
-        <v>10900</v>
+        <v>197000</v>
       </c>
       <c r="M14" t="n">
-        <v>8730</v>
+        <v>180800</v>
       </c>
       <c r="N14" t="n">
-        <v>0.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>31554032230</v>
+        <v>1533063411800</v>
       </c>
       <c r="P14" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3200</v>
+        <v>71000</v>
       </c>
       <c r="R14" t="n">
-        <v>-40000</v>
+        <v>-1382000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>-119000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>오너 리스크 및 IR 부실에 대한 불만. 주주 환원 정책 불확실성.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['오너 리스크', 'IR 부실', '주주 환원']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G15" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H15" t="n">
         <v>2.2</v>
@@ -1806,7 +1806,7 @@
         <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>173991427504</v>
+        <v>174546678404</v>
       </c>
       <c r="P15" t="n">
         <v>8100</v>
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G16" t="n">
-        <v>2921</v>
+        <v>2870</v>
       </c>
       <c r="H16" t="n">
         <v>46.19</v>
@@ -1898,7 +1898,7 @@
         <v>46.15</v>
       </c>
       <c r="O16" t="n">
-        <v>5283799379250</v>
+        <v>5360039658000</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이사회 결정에 대한 불만 고조. 주주 환원 지연 및 증여세 관련 의혹 제기.</t>
+          <t>이사회 결정에 따른 주주환원 지연 및 증여세 관련 의혹 제기. 경영진 비판과 코리아 디스카운트 자초 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주 환원', '증여세', '이사회 결정']</t>
+          <t>['주주환원', '증여세', '이사회']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15730</v>
+        <v>15700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-4.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F17" t="n">
         <v>138</v>
       </c>
       <c r="G17" t="n">
-        <v>701</v>
+        <v>724</v>
       </c>
       <c r="H17" t="n">
         <v>28.07</v>
@@ -1990,7 +1990,7 @@
         <v>28.03</v>
       </c>
       <c r="O17" t="n">
-        <v>78765790300</v>
+        <v>80115276060</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 및 수주 공시에도 불구하고 주가 하락 지속. 조선주 동반 약세.</t>
+          <t>실적 및 수주 공시 발표에도 주가 하락 지속. 순이익 컨센서스 대비 증가. 조선주 비교 속에서 부진.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적 발표', '수주 공시', '주가 하락']</t>
+          <t>['실적', '수주', '순이익']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1976</v>
+        <v>1993</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-5.10%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>18945599499</v>
+        <v>19269373709</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56600</v>
+        <v>56500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.82%</t>
+          <t>'-7.98%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G19" t="n">
-        <v>2270</v>
+        <v>2284</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>424364076650</v>
+        <v>427618042550</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 입찰 관련 허위 기사 논란. 해명 공시 후 주가 회복 기대.</t>
+          <t>허위 기사 및 풍문에 대한 회사 해명 공시 발표. 계약 관련 문제없음 주장 및 기자 고소 요구.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['체코 원전', '허위 기사', '해명 공시']</t>
+          <t>['해명공시', '풍문', '계약']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23600</v>
+        <v>23650</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-11.61%</t>
+          <t>'-11.42%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="F20" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G20" t="n">
-        <v>836</v>
+        <v>870</v>
       </c>
       <c r="H20" t="n">
         <v>12.23</v>
@@ -2266,7 +2266,7 @@
         <v>12.3</v>
       </c>
       <c r="O20" t="n">
-        <v>143932163275</v>
+        <v>149804009025</v>
       </c>
       <c r="P20" t="n">
         <v>59300</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>실적 발표 후 주가 하락에 대한 불만. 미 증시 태양광 하락 영향.</t>
+          <t>실적 발표 예정. 태양광 시장 전망에도 불구하고 실적 하회 및 외인 매도세 관측. 투자 의견 분분.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적 발표', '주가 하락', '태양광']</t>
+          <t>['실적발표', '태양광', '영업이익']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16800</v>
+        <v>17000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-12.55%</t>
+          <t>'-11.50%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.46</v>
       </c>
       <c r="E21" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F21" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G21" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="H21" t="n">
         <v>0.65</v>
@@ -2358,7 +2358,7 @@
         <v>1.11</v>
       </c>
       <c r="O21" t="n">
-        <v>105807335690</v>
+        <v>106480084815</v>
       </c>
       <c r="P21" t="n">
         <v>28800</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-17.90%</t>
+          <t>'-18.09%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F22" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>17550097863</v>
+        <v>17704366222</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11670</v>
+        <v>11640</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-18.22%</t>
+          <t>'-18.43%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G23" t="n">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="H23" t="n">
         <v>9.6</v>
@@ -2542,7 +2542,7 @@
         <v>9.83</v>
       </c>
       <c r="O23" t="n">
-        <v>361504485405</v>
+        <v>364248831770</v>
       </c>
       <c r="P23" t="n">
         <v>40350</v>

--- a/data/trending_integrated_20261029_15.xlsx
+++ b/data/trending_integrated_20261029_15.xlsx
@@ -610,7 +610,7 @@
         <v>1.02</v>
       </c>
       <c r="O2" t="n">
-        <v>8562406320</v>
+        <v>8570193960</v>
       </c>
       <c r="P2" t="n">
         <v>10200</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49200</v>
+        <v>49100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+22.39%</t>
+          <t>'+22.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F3" t="n">
         <v>112</v>
       </c>
       <c r="G3" t="n">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="H3" t="n">
         <v>24.64</v>
@@ -702,7 +702,7 @@
         <v>24.63</v>
       </c>
       <c r="O3" t="n">
-        <v>109033959475</v>
+        <v>110415289775</v>
       </c>
       <c r="P3" t="n">
         <v>97900</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9390</v>
+        <v>9440</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+17.52%</t>
+          <t>'+18.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G4" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H4" t="n">
         <v>17.97</v>
@@ -794,7 +794,7 @@
         <v>18.64</v>
       </c>
       <c r="O4" t="n">
-        <v>144937493540</v>
+        <v>145591883780</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -860,7 +860,7 @@
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H5" t="n">
         <v>5.8</v>
@@ -886,7 +886,7 @@
         <v>6.54</v>
       </c>
       <c r="O5" t="n">
-        <v>121643732600</v>
+        <v>122304024650</v>
       </c>
       <c r="P5" t="n">
         <v>126600</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7880</v>
+        <v>7900</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+5.77%</t>
+          <t>'+6.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.04</v>
       </c>
       <c r="E6" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F6" t="n">
         <v>99</v>
       </c>
       <c r="G6" t="n">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="H6" t="n">
         <v>0.42</v>
@@ -978,7 +978,7 @@
         <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>115168674705</v>
+        <v>115465264405</v>
       </c>
       <c r="P6" t="n">
         <v>10300</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>광주 반도체 테마 편입 및 외국인 매수세 유입. 단기 급등 후 차익 실현.</t>
+          <t>하이닉스 물량 완판 및 반도체 속도전 돌입. 외국인 및 기타법인 매수 유입. 10배 텐베거 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['광주 반도체', '외국인 매수', '테마주']</t>
+          <t>['반도체', '외국인매수', '텐베거']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14950</v>
+        <v>14980</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.89%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="H7" t="n">
         <v>8.050000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>64405912605</v>
+        <v>64786928905</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>의료 AI 관련 미국 시장 급등 영향. 매수 구간 진입 및 공매도 청산 기대감.</t>
+          <t>미국 의료 AI 섹터 급등 및 템퍼스AI 긍정적 흐름. 14,500원 이하 매수 구간으로 판단. 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료AI', '나스닥', '공매도']</t>
+          <t>['의료AI', '템퍼스AI', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1520000</v>
+        <v>1526000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.22%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G8" t="n">
-        <v>1996</v>
+        <v>2044</v>
       </c>
       <c r="H8" t="n">
         <v>48.66</v>
@@ -1162,7 +1162,7 @@
         <v>48.61</v>
       </c>
       <c r="O8" t="n">
-        <v>6389597865500</v>
+        <v>6670651967500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 결정 및 외국인 연일 매수세 유입. 공매도 불가 및 주주 친화적 결정 긍정적 평가.</t>
+          <t>자사주 매입 결정. 공매도 불가 예상 및 외국인 연속 매수. 아마존 호실적에 따른 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '외국인매수', '공매도']</t>
+          <t>['자사주매입', '공매도', '외국인매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1254,7 +1254,7 @@
         <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>112478279900</v>
+        <v>112876468900</v>
       </c>
       <c r="P9" t="n">
         <v>59600</v>
@@ -1299,83 +1299,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15020</v>
+        <v>538000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.75%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.46</v>
+        <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>169</v>
+        <v>398</v>
       </c>
       <c r="F10" t="n">
-        <v>99</v>
+        <v>191</v>
       </c>
       <c r="G10" t="n">
-        <v>1044</v>
+        <v>1911</v>
       </c>
       <c r="H10" t="n">
-        <v>3.33</v>
+        <v>24.78</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14980</v>
+        <v>534000</v>
       </c>
       <c r="K10" t="n">
-        <v>15120</v>
+        <v>546000</v>
       </c>
       <c r="L10" t="n">
-        <v>15950</v>
+        <v>563000</v>
       </c>
       <c r="M10" t="n">
-        <v>14600</v>
+        <v>512000</v>
       </c>
       <c r="N10" t="n">
-        <v>2.87</v>
+        <v>24.86</v>
       </c>
       <c r="O10" t="n">
-        <v>155172036050</v>
+        <v>597023966500</v>
       </c>
       <c r="P10" t="n">
-        <v>31500</v>
+        <v>723000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1819</v>
+        <v>259000</v>
       </c>
       <c r="R10" t="n">
-        <v>-444000</v>
+        <v>-36000</v>
       </c>
       <c r="S10" t="n">
-        <v>44000</v>
+        <v>35000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메타 및 유리기판 관련 뉴스 부각. 삼성전자 인수 기대감 및 연기금 매집.</t>
+          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '삼성전자', '연기금']</t>
+          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>006400</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>535000</v>
+        <v>15030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.19%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.08</v>
+        <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>397</v>
+        <v>170</v>
       </c>
       <c r="F11" t="n">
-        <v>191</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>1907</v>
+        <v>1048</v>
       </c>
       <c r="H11" t="n">
-        <v>24.78</v>
+        <v>3.33</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>534000</v>
+        <v>14980</v>
       </c>
       <c r="K11" t="n">
-        <v>546000</v>
+        <v>15120</v>
       </c>
       <c r="L11" t="n">
-        <v>563000</v>
+        <v>15950</v>
       </c>
       <c r="M11" t="n">
-        <v>512000</v>
+        <v>14600</v>
       </c>
       <c r="N11" t="n">
-        <v>24.86</v>
+        <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>583257084500</v>
+        <v>155559764960</v>
       </c>
       <c r="P11" t="n">
-        <v>723000</v>
+        <v>31500</v>
       </c>
       <c r="Q11" t="n">
-        <v>259000</v>
+        <v>1819</v>
       </c>
       <c r="R11" t="n">
-        <v>-36000</v>
+        <v>-444000</v>
       </c>
       <c r="S11" t="n">
-        <v>35000</v>
+        <v>44000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>컨퍼런스콜 통해 전고체 배터리 상용화 및 4분기 사상 최대 실적 전망 확인. 미래 성장성 긍정적.</t>
+          <t>메타 관련 뉴스 및 3분기 예상 실적 호조 전망. 루멘텀 인수 및 미국장 광통신주 급등 영향.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['전고체 배터리', '컨퍼런스콜', '사상 최대 실적']</t>
+          <t>['메타', '유리기판', '광통신']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1498,13 +1498,13 @@
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="n">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>196162126850</v>
+        <v>201038986450</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8880</v>
+        <v>183900</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.27%</t>
+          <t>'-3.26%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.37</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>197</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>131</v>
       </c>
       <c r="G13" t="n">
-        <v>210</v>
+        <v>647</v>
       </c>
       <c r="H13" t="n">
-        <v>0.37</v>
+        <v>75</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9180</v>
+        <v>190100</v>
       </c>
       <c r="K13" t="n">
-        <v>9200</v>
+        <v>189400</v>
       </c>
       <c r="L13" t="n">
-        <v>10900</v>
+        <v>197000</v>
       </c>
       <c r="M13" t="n">
-        <v>8730</v>
+        <v>180800</v>
       </c>
       <c r="N13" t="n">
-        <v>0.74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>31680390985</v>
+        <v>1573377602000</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>243500</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>71000</v>
       </c>
       <c r="R13" t="n">
-        <v>-40000</v>
+        <v>-1382000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>-119000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
+          <t>오너 리스크 및 IR 부실에 대한 불만. 주주 환원 정책 불확실성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
+          <t>['오너 리스크', 'IR 부실', '주주 환원']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>183800</v>
+        <v>8870</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.31%</t>
+          <t>'-3.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>-0.37</v>
       </c>
       <c r="E14" t="n">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>646</v>
+        <v>211</v>
       </c>
       <c r="H14" t="n">
-        <v>75</v>
+        <v>0.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>190100</v>
+        <v>9180</v>
       </c>
       <c r="K14" t="n">
-        <v>189400</v>
+        <v>9200</v>
       </c>
       <c r="L14" t="n">
-        <v>197000</v>
+        <v>10900</v>
       </c>
       <c r="M14" t="n">
-        <v>180800</v>
+        <v>8730</v>
       </c>
       <c r="N14" t="n">
-        <v>74.90000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>1533063411800</v>
+        <v>31758988055</v>
       </c>
       <c r="P14" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q14" t="n">
-        <v>71000</v>
+        <v>3200</v>
       </c>
       <c r="R14" t="n">
-        <v>-1382000</v>
+        <v>-40000</v>
       </c>
       <c r="S14" t="n">
-        <v>-119000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>오너 리스크 및 IR 부실에 대한 불만. 주주 환원 정책 불확실성.</t>
+          <t>주가 조작 및 경영진에 대한 강한 불신 표출. 주가 하락 및 거래량 부진에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['오너 리스크', 'IR 부실', '주주 환원']</t>
+          <t>['주가 조작', '경영진 불신', '거래량 부진']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4030</v>
+        <v>4040</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.93%</t>
+          <t>'-3.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F15" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G15" t="n">
         <v>422</v>
@@ -1806,7 +1806,7 @@
         <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>174546678404</v>
+        <v>174920515764</v>
       </c>
       <c r="P15" t="n">
         <v>8100</v>
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="G16" t="n">
-        <v>2870</v>
+        <v>3033</v>
       </c>
       <c r="H16" t="n">
         <v>46.19</v>
@@ -1898,7 +1898,7 @@
         <v>46.15</v>
       </c>
       <c r="O16" t="n">
-        <v>5360039658000</v>
+        <v>5689761770000</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이사회 결정에 따른 주주환원 지연 및 증여세 관련 의혹 제기. 경영진 비판과 코리아 디스카운트 자초 지적.</t>
+          <t>이사회 해명 요구 및 주주환원 지연, 증여세 회피 의혹 제기. 컨콜 내용에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '증여세', '이사회']</t>
+          <t>['주주환원', '증여세', '컨콜']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15700</v>
+        <v>15720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.91%</t>
+          <t>'-4.78%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="F17" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="H17" t="n">
         <v>28.07</v>
@@ -1990,7 +1990,7 @@
         <v>28.03</v>
       </c>
       <c r="O17" t="n">
-        <v>80115276060</v>
+        <v>84089386380</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2050,13 +2050,13 @@
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>19269373709</v>
+        <v>19437648678</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>56500</v>
+        <v>56700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-7.98%</t>
+          <t>'-7.65%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>532</v>
       </c>
       <c r="G19" t="n">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>427618042550</v>
+        <v>437238331550</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>허위 기사 및 풍문에 대한 회사 해명 공시 발표. 계약 관련 문제없음 주장 및 기자 고소 요구.</t>
+          <t>체코 원전 수주 관련 허위 기사 및 풍문에 대한 해명 공시 발표. 기자 고소 및 악의적 보도 비판.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['해명공시', '풍문', '계약']</t>
+          <t>['해명공시', '풍문', '기사']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2219,79 +2219,79 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한화솔루션</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23650</v>
+        <v>17000</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-11.42%</t>
+          <t>'-11.50%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="E20" t="n">
-        <v>356</v>
+        <v>202</v>
       </c>
       <c r="F20" t="n">
+        <v>73</v>
+      </c>
+      <c r="G20" t="n">
         <v>189</v>
       </c>
-      <c r="G20" t="n">
-        <v>870</v>
-      </c>
       <c r="H20" t="n">
-        <v>12.23</v>
+        <v>0.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>26700</v>
+        <v>19210</v>
       </c>
       <c r="K20" t="n">
-        <v>26350</v>
+        <v>19010</v>
       </c>
       <c r="L20" t="n">
-        <v>26600</v>
+        <v>19840</v>
       </c>
       <c r="M20" t="n">
-        <v>23300</v>
+        <v>16280</v>
       </c>
       <c r="N20" t="n">
-        <v>12.3</v>
+        <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>149804009025</v>
+        <v>106887540815</v>
       </c>
       <c r="P20" t="n">
-        <v>59300</v>
+        <v>28800</v>
       </c>
       <c r="Q20" t="n">
-        <v>22000</v>
+        <v>11550</v>
       </c>
       <c r="R20" t="n">
-        <v>-394000</v>
+        <v>20000</v>
       </c>
       <c r="S20" t="n">
-        <v>-18000</v>
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>실적 발표 예정. 태양광 시장 전망에도 불구하고 실적 하회 및 외인 매도세 관측. 투자 의견 분분.</t>
+          <t>보호예수 물량 출회 우려. 하한가 및 폭락 가능성 언급. 주포의 올릴 이유 부재 지적.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적발표', '태양광', '영업이익']</t>
+          <t>['보호예수', '폭락', '주포']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,86 +2304,86 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>009830</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>한화솔루션</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17000</v>
+        <v>23600</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-11.50%</t>
+          <t>'-11.61%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.46</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>208</v>
+        <v>372</v>
       </c>
       <c r="F21" t="n">
-        <v>73</v>
+        <v>199</v>
       </c>
       <c r="G21" t="n">
-        <v>198</v>
+        <v>939</v>
       </c>
       <c r="H21" t="n">
-        <v>0.65</v>
+        <v>12.23</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>19210</v>
+        <v>26700</v>
       </c>
       <c r="K21" t="n">
-        <v>19010</v>
+        <v>26350</v>
       </c>
       <c r="L21" t="n">
-        <v>19840</v>
+        <v>26600</v>
       </c>
       <c r="M21" t="n">
-        <v>16280</v>
+        <v>23300</v>
       </c>
       <c r="N21" t="n">
-        <v>1.11</v>
+        <v>12.3</v>
       </c>
       <c r="O21" t="n">
-        <v>106480084815</v>
+        <v>152640068225</v>
       </c>
       <c r="P21" t="n">
-        <v>28800</v>
+        <v>59300</v>
       </c>
       <c r="Q21" t="n">
-        <v>11550</v>
+        <v>22000</v>
       </c>
       <c r="R21" t="n">
-        <v>20000</v>
+        <v>-394000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>보호예수 물량 출회에 따른 급락 및 하락 전망. 주포의 의도에 대한 의구심.</t>
+          <t>실적 발표 예정. 미장 태양광 하락과 연동되는 모습. 예상치 하회한 3분기 영업이익에 대한 실망감.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['보호예수', '하락', '주포']</t>
+          <t>['실적발표', '영업이익', '태양광']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>179880</t>
+          <t>009830</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2105</v>
+        <v>2095</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-18.09%</t>
+          <t>'-18.48%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G22" t="n">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>17704366222</v>
+        <v>17819346107</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>11640</v>
+        <v>11620</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-18.43%</t>
+          <t>'-18.57%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="G23" t="n">
-        <v>2414</v>
+        <v>2407</v>
       </c>
       <c r="H23" t="n">
         <v>9.6</v>
@@ -2542,7 +2542,7 @@
         <v>9.83</v>
       </c>
       <c r="O23" t="n">
-        <v>364248831770</v>
+        <v>365591185790</v>
       </c>
       <c r="P23" t="n">
         <v>40350</v>

--- a/data/trending_integrated_20261029_15.xlsx
+++ b/data/trending_integrated_20261029_15.xlsx
@@ -578,7 +578,7 @@
         <v>-0.4</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
         <v>27</v>
@@ -670,13 +670,13 @@
         <v>0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3" t="n">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="H3" t="n">
         <v>24.64</v>
@@ -702,7 +702,7 @@
         <v>24.63</v>
       </c>
       <c r="O3" t="n">
-        <v>110415289775</v>
+        <v>110425797175</v>
       </c>
       <c r="P3" t="n">
         <v>97900</v>
@@ -762,13 +762,13 @@
         <v>-0.67</v>
       </c>
       <c r="E4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H4" t="n">
         <v>17.97</v>
@@ -794,7 +794,7 @@
         <v>18.64</v>
       </c>
       <c r="O4" t="n">
-        <v>145591883780</v>
+        <v>145644086980</v>
       </c>
       <c r="P4" t="n">
         <v>22450</v>
@@ -854,13 +854,13 @@
         <v>-0.74</v>
       </c>
       <c r="E5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H5" t="n">
         <v>5.8</v>
@@ -886,7 +886,7 @@
         <v>6.54</v>
       </c>
       <c r="O5" t="n">
-        <v>122304024650</v>
+        <v>122333587700</v>
       </c>
       <c r="P5" t="n">
         <v>126600</v>
@@ -946,13 +946,13 @@
         <v>-1.04</v>
       </c>
       <c r="E6" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F6" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G6" t="n">
-        <v>478</v>
+        <v>493</v>
       </c>
       <c r="H6" t="n">
         <v>0.42</v>
@@ -978,7 +978,7 @@
         <v>1.46</v>
       </c>
       <c r="O6" t="n">
-        <v>115465264405</v>
+        <v>115505688705</v>
       </c>
       <c r="P6" t="n">
         <v>10300</v>
@@ -1038,13 +1038,13 @@
         <v>-0.06</v>
       </c>
       <c r="E7" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G7" t="n">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="H7" t="n">
         <v>8.050000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>64786928905</v>
+        <v>64787198545</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>미국 의료 AI 섹터 급등 및 템퍼스AI 긍정적 흐름. 14,500원 이하 매수 구간으로 판단. 공매도 세력 비판.</t>
+          <t>의료 AI 관련 미국 시장 급등 동반, 일부 긍정적 전망 속 공매도 관련 논란.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료AI', '템퍼스AI', '공매도']</t>
+          <t>['의료AI', '미국장', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G8" t="n">
-        <v>2044</v>
+        <v>2088</v>
       </c>
       <c r="H8" t="n">
         <v>48.66</v>
@@ -1162,7 +1162,7 @@
         <v>48.61</v>
       </c>
       <c r="O8" t="n">
-        <v>6670651967500</v>
+        <v>6673516269500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>자사주 매입 결정. 공매도 불가 예상 및 외국인 연속 매수. 아마존 호실적에 따른 기대감.</t>
+          <t>자사주 매입 및 외국인 연속 매수에 따른 주가 상승 기대. 삼성전자와의 비교 우위 부각.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['자사주매입', '공매도', '외국인매수']</t>
+          <t>['자사주매입', '외국인매수', '실적']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,10 +1222,10 @@
         <v>0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G9" t="n">
         <v>81</v>
@@ -1254,7 +1254,7 @@
         <v>1.73</v>
       </c>
       <c r="O9" t="n">
-        <v>112876468900</v>
+        <v>112902266650</v>
       </c>
       <c r="P9" t="n">
         <v>59600</v>
@@ -1314,13 +1314,13 @@
         <v>-0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F10" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G10" t="n">
-        <v>1911</v>
+        <v>1932</v>
       </c>
       <c r="H10" t="n">
         <v>24.78</v>
@@ -1346,7 +1346,7 @@
         <v>24.86</v>
       </c>
       <c r="O10" t="n">
-        <v>597023966500</v>
+        <v>597041720500</v>
       </c>
       <c r="P10" t="n">
         <v>723000</v>
@@ -1406,13 +1406,13 @@
         <v>0.46</v>
       </c>
       <c r="E11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F11" t="n">
         <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="H11" t="n">
         <v>3.33</v>
@@ -1438,7 +1438,7 @@
         <v>2.87</v>
       </c>
       <c r="O11" t="n">
-        <v>155559764960</v>
+        <v>155578958270</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1498,13 +1498,13 @@
         <v>0.54</v>
       </c>
       <c r="E12" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G12" t="n">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="H12" t="n">
         <v>41.55</v>
@@ -1530,7 +1530,7 @@
         <v>41.01</v>
       </c>
       <c r="O12" t="n">
-        <v>201038986450</v>
+        <v>201069695650</v>
       </c>
       <c r="P12" t="n">
         <v>67300</v>
@@ -1590,13 +1590,13 @@
         <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F13" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G13" t="n">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="H13" t="n">
         <v>75</v>
@@ -1622,7 +1622,7 @@
         <v>74.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1573377602000</v>
+        <v>1573571432600</v>
       </c>
       <c r="P13" t="n">
         <v>243500</v>
@@ -1688,7 +1688,7 @@
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H14" t="n">
         <v>0.37</v>
@@ -1714,7 +1714,7 @@
         <v>0.74</v>
       </c>
       <c r="O14" t="n">
-        <v>31758988055</v>
+        <v>31760105675</v>
       </c>
       <c r="P14" t="n">
         <v>19380</v>
@@ -1806,7 +1806,7 @@
         <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>174920515764</v>
+        <v>174967088884</v>
       </c>
       <c r="P15" t="n">
         <v>8100</v>
@@ -1872,7 +1872,7 @@
         <v>528</v>
       </c>
       <c r="G16" t="n">
-        <v>3033</v>
+        <v>3241</v>
       </c>
       <c r="H16" t="n">
         <v>46.19</v>
@@ -1898,7 +1898,7 @@
         <v>46.15</v>
       </c>
       <c r="O16" t="n">
-        <v>5689761770000</v>
+        <v>5693326914000</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>이사회 해명 요구 및 주주환원 지연, 증여세 회피 의혹 제기. 컨콜 내용에 대한 불만 표출.</t>
+          <t>주주환원 지연 및 증여세 회피 의혹으로 인한 경영진 비판. IR팀 교체 요구.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주주환원', '증여세', '컨콜']</t>
+          <t>['주주환원', '증여세', '이사회']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1958,13 +1958,13 @@
         <v>0.04</v>
       </c>
       <c r="E17" t="n">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F17" t="n">
         <v>141</v>
       </c>
       <c r="G17" t="n">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H17" t="n">
         <v>28.07</v>
@@ -1990,7 +1990,7 @@
         <v>28.03</v>
       </c>
       <c r="O17" t="n">
-        <v>84089386380</v>
+        <v>84089732220</v>
       </c>
       <c r="P17" t="n">
         <v>35350</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>실적 및 수주 공시 발표에도 주가 하락 지속. 순이익 컨센서스 대비 증가. 조선주 비교 속에서 부진.</t>
+          <t>실적 및 수주에도 불구하고 주가 하락 지속. 연기금 매도세 및 공매도 금지 요구.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['실적', '수주', '순이익']</t>
+          <t>['실적', '수주', '주가하락']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>0.28</v>
       </c>
       <c r="E18" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F18" t="n">
         <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="H18" t="n">
         <v>5.35</v>
@@ -2082,7 +2082,7 @@
         <v>5.07</v>
       </c>
       <c r="O18" t="n">
-        <v>19437648678</v>
+        <v>19443017820</v>
       </c>
       <c r="P18" t="n">
         <v>4980</v>
@@ -2145,10 +2145,10 @@
         <v>800</v>
       </c>
       <c r="F19" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G19" t="n">
-        <v>2285</v>
+        <v>2338</v>
       </c>
       <c r="H19" t="n">
         <v>22.34</v>
@@ -2174,7 +2174,7 @@
         <v>22.32</v>
       </c>
       <c r="O19" t="n">
-        <v>437238331550</v>
+        <v>437240089250</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>체코 원전 수주 관련 허위 기사 및 풍문에 대한 해명 공시 발표. 기자 고소 및 악의적 보도 비판.</t>
+          <t>체코 원전 관련 자극적인 기사 보도에 따른 주가 하락. 해명 공시 통해 일부 회복 기대.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['해명공시', '풍문', '기사']</t>
+          <t>['체코원전', '해명공시', '허위기사']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2266,7 +2266,7 @@
         <v>1.11</v>
       </c>
       <c r="O20" t="n">
-        <v>106887540815</v>
+        <v>106897978815</v>
       </c>
       <c r="P20" t="n">
         <v>28800</v>
@@ -2326,13 +2326,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F21" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G21" t="n">
-        <v>939</v>
+        <v>999</v>
       </c>
       <c r="H21" t="n">
         <v>12.23</v>
@@ -2358,7 +2358,7 @@
         <v>12.3</v>
       </c>
       <c r="O21" t="n">
-        <v>152640068225</v>
+        <v>152822732225</v>
       </c>
       <c r="P21" t="n">
         <v>59300</v>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>실적 발표 예정. 미장 태양광 하락과 연동되는 모습. 예상치 하회한 3분기 영업이익에 대한 실망감.</t>
+          <t>실적 발표 예정, 태양광 업황 부진 및 외인 매도세에 따른 주가 하락 우려. 일부 분할 매수 권고.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['실적발표', '영업이익', '태양광']</t>
+          <t>['실적발표', '태양광', '외인매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2418,13 +2418,13 @@
         <v>-0.47</v>
       </c>
       <c r="E22" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F22" t="n">
         <v>64</v>
       </c>
       <c r="G22" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H22" t="n">
         <v>1.22</v>
@@ -2450,7 +2450,7 @@
         <v>1.69</v>
       </c>
       <c r="O22" t="n">
-        <v>17819346107</v>
+        <v>17821126857</v>
       </c>
       <c r="P22" t="n">
         <v>2965</v>
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G23" t="n">
-        <v>2407</v>
+        <v>2425</v>
       </c>
       <c r="H23" t="n">
         <v>9.6</v>
@@ -2542,7 +2542,7 @@
         <v>9.83</v>
       </c>
       <c r="O23" t="n">
-        <v>365591185790</v>
+        <v>365717413850</v>
       </c>
       <c r="P23" t="n">
         <v>40350</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>체코 원전 수주 불발에 따른 반사 이익 기대감. 정치권 개입 및 협상 과정에 대한 불만 표출.</t>
+          <t>체코 원전 사업 재협상 지연에 따른 주가 하락 우려. 다만, 외인 매수세 유입 관측.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['체코 원전', '수주 불발', '정치권 개입']</t>
+          <t>['체코원전', '재협상', '외인매수']</t>
         </is>
       </c>
       <c r="X23" t="n">
